--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_07-07-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_07-07-2025.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£1,017.24</t>
+          <t>£10.81</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>£919.24</t>
+          <t>£11.73</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£782.04</t>
+          <t>£14.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£762.44</t>
+          <t>£16.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£764.40</t>
+          <t>£19.50</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£682.08</t>
+          <t>£21.75</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£723.24</t>
+          <t>£23.06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£697.76</t>
+          <t>£25.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£644.84</t>
+          <t>£27.42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£666.40</t>
+          <t>£28.33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>£646.80</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£605.64</t>
+          <t>£34.33</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£723.24</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£654.64</t>
+          <t>£37.11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£627.20</t>
+          <t>£40.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>£674.24</t>
+          <t>£43.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
